--- a/results/Optimization.xlsx
+++ b/results/Optimization.xlsx
@@ -518,22 +518,22 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>70.51000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.87</v>
+        <v>7.94</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-7.5</v>
+        <v>-7.67</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>260.43</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="3">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>69.23</v>
+        <v>66.27</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>8.050000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-7.99</v>
+        <v>-8.08</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>243.2</v>
+        <v>224.63</v>
       </c>
     </row>
     <row r="4">
@@ -578,22 +578,22 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>70.51000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.08</v>
+        <v>7.16</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-7.5</v>
+        <v>-7.67</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>217.07</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="5">
@@ -608,142 +608,142 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.79</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-7.81</v>
+        <v>-8.34</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>213.61</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>68.56999999999999</v>
+        <v>55.68</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7.9</v>
+        <v>8.57</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-8.32</v>
+        <v>-6.13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>196.38</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>57.32</v>
+        <v>65.33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8.57</v>
+        <v>8.07</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-6.04</v>
+        <v>-8.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>191.58</v>
+        <v>167.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>70</v>
+        <v>54.55</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6.99</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-7.81</v>
+        <v>-6.46</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>178.71</v>
+        <v>167.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>56.1</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.08</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-6.4</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>174.35</v>
+        <v>163.81</v>
       </c>
     </row>
     <row r="10">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>57.32</v>
+        <v>56.82</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>7.83</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-6.04</v>
+        <v>-6.12</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>156.68</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="11">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>72.5</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5.33</v>
+        <v>5.43</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-7.47</v>
+        <v>-7.62</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>144.95</v>
+        <v>143.86</v>
       </c>
     </row>
     <row r="12">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.53</v>
+        <v>63.44</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5.91</v>
+        <v>5.95</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-6.15</v>
+        <v>-6.31</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>128.63</v>
+        <v>136.76</v>
       </c>
     </row>
     <row r="13">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>72.22</v>
+        <v>70.89</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5.31</v>
+        <v>5.42</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-7.68</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>122.68</v>
+        <v>116.16</v>
       </c>
     </row>
     <row r="14">
@@ -878,22 +878,22 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>39.58</v>
+        <v>37.86</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9.1</v>
+        <v>9.17</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-4.22</v>
+        <v>-4.31</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>100.87</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="15">
@@ -908,22 +908,22 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>37.5</v>
+        <v>35.92</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-4.46</v>
+        <v>-4.52</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>63.83</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="16">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>39.58</v>
+        <v>37.86</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-4.22</v>
+        <v>-4.31</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>60.37</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="17">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>45.92</v>
+        <v>45.37</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5.94</v>
+        <v>5.92</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-4.27</v>
+        <v>-4.32</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>41.13</v>
+        <v>35.01</v>
       </c>
     </row>
   </sheetData>

--- a/results/Optimization.xlsx
+++ b/results/Optimization.xlsx
@@ -461,7 +461,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,14 +502,14 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Total Return (%)</t>
+          <t>Sum of Trade Returns (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -518,52 +518,52 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>67.47</v>
+        <v>71.88</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.94</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-7.67</v>
+        <v>-8.74</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>237.78</v>
+        <v>110.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>66.27</v>
+        <v>72.73</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.09</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-8.08</v>
+        <v>-8.74</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>224.63</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>68.67</v>
+        <v>63.16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.16</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-7.67</v>
+        <v>-7.98</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>208.58</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -608,52 +608,52 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>66.67</v>
+        <v>52.17</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7.79</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-8.34</v>
+        <v>-6.17</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>181</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>55.68</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8.57</v>
+        <v>7.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-6.13</v>
+        <v>-7.98</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>180.79</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="7">
@@ -668,58 +668,58 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>65.33</v>
+        <v>66.67</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8.07</v>
+        <v>7.75</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-8.75</v>
+        <v>-9.77</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>167.86</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="n">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>54.55</v>
+        <v>73.53</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-6.46</v>
+        <v>-8.74</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>167.64</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -728,52 +728,52 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>68</v>
+        <v>53.19</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7.08</v>
+        <v>7.52</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-8.210000000000001</v>
+        <v>-6.17</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>163.81</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>56.82</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7.83</v>
+        <v>5.45</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-6.12</v>
+        <v>-7.98</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>158.63</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="11">
@@ -784,26 +784,26 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>70.79000000000001</v>
+        <v>58.33</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5.43</v>
+        <v>7.84</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-7.62</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>143.86</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="12">
@@ -818,82 +818,82 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63.44</v>
+        <v>57.14</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5.95</v>
+        <v>5.79</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-6.31</v>
+        <v>-6.19</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>136.76</v>
+        <v>32.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>70.89</v>
+        <v>33.96</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5.42</v>
+        <v>10.05</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-8.140000000000001</v>
+        <v>-4.31</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>116.16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>37.86</v>
+        <v>47.73</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9.17</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-4.31</v>
+        <v>-6.73</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>81.73</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="15">
@@ -904,26 +904,26 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>35.92</v>
+        <v>35.19</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9.390000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-4.52</v>
+        <v>-4.31</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>48.78</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
@@ -934,26 +934,26 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>37.86</v>
+        <v>40</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8.039999999999999</v>
+        <v>6.14</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-4.31</v>
+        <v>-4.35</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>37.77</v>
+        <v>-8.42</v>
       </c>
     </row>
     <row r="17">
@@ -964,26 +964,26 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>45.37</v>
+        <v>27.45</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5.92</v>
+        <v>9.34</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-4.32</v>
+        <v>-4.69</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>35.01</v>
+        <v>-42.86</v>
       </c>
     </row>
   </sheetData>

--- a/results/Optimization.xlsx
+++ b/results/Optimization.xlsx
@@ -4,22 +4,26 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grid_Search" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Grid_Search'!$A$1:$H$17</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +32,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A1A19"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B6A66"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006300"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A19"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006B6A66"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +91,20 @@
         <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4E6"/>
+        <bgColor rgb="00E6F4E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5F8"/>
+        <bgColor rgb="00F3F5F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -56,36 +114,81 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="00D4D8DE"/>
       </left>
       <right style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="00D4D8DE"/>
       </right>
       <top style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="00D4D8DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="00D4D8DE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00EB6834"/>
+      </left>
+      <right style="thick">
+        <color rgb="00EB6834"/>
+      </right>
+      <top style="thick">
+        <color rgb="00EB6834"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00EB6834"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,15 +551,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A78D6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -464,7 +568,7 @@
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
@@ -517,22 +621,22 @@
           <t>12%</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>71.88</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>-8.74</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>110.33</v>
       </c>
     </row>
@@ -547,22 +651,22 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>72.73</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>7.09</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>-8.74</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>2.17</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>91.59999999999999</v>
       </c>
     </row>
@@ -577,53 +681,53 @@
           <t>12%</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>63.16</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>-7.98</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>1.78</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>86.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-6.17</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>71.01000000000001</v>
+      <c r="C5" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>56.56</v>
       </c>
     </row>
     <row r="6">
@@ -637,22 +741,22 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>-7.98</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>68.12</v>
       </c>
     </row>
@@ -667,53 +771,53 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>66.67</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>7.75</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>-9.77</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>1.59</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>57.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>73.53</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-8.74</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>56.56</v>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -727,22 +831,22 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>53.19</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>7.52</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>-6.17</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>1.39</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>52.29</v>
       </c>
     </row>
@@ -757,22 +861,22 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>65.84999999999999</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>-7.98</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>1.32</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>35.35</v>
       </c>
     </row>
@@ -787,22 +891,22 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>58.33</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>7.84</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <v>-8.720000000000001</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>1.26</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>33.79</v>
       </c>
     </row>
@@ -817,22 +921,22 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>57.14</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>5.79</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>-6.19</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>1.25</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>32.19</v>
       </c>
     </row>
@@ -847,22 +951,22 @@
           <t>12%</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>33.96</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>10.05</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -877,22 +981,22 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>47.73</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>-6.73</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>1.12</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>17.96</v>
       </c>
     </row>
@@ -907,22 +1011,22 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>35.19</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <v>-4.31</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>1.05</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>6.95</v>
       </c>
     </row>
@@ -937,22 +1041,22 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>6.14</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>-4.35</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <v>-8.42</v>
       </c>
     </row>
@@ -967,35 +1071,36 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>27.45</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>9.34</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <v>-42.86</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H17"/>
   <conditionalFormatting sqref="D2:D17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="00FFC7CE"/>
-        <color rgb="00FFE699"/>
-        <color rgb="00C6EFCE"/>
+        <color rgb="00F8D0D0"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00CDE7CD"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -1005,9 +1110,9 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="00FFC7CE"/>
-        <color rgb="00FFE699"/>
-        <color rgb="00C6EFCE"/>
+        <color rgb="00F8D0D0"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00CDE7CD"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -1017,12 +1122,609 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="00FFC7CE"/>
-        <color rgb="00FFE699"/>
-        <color rgb="00C6EFCE"/>
+        <color rgb="00F8D0D0"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00CDE7CD"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E78"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Stop-loss / take-profit grid search</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Tuned on 01 Jan 2024 to 31 Dec 2024. The chosen pair is then tested on 01 Jan 2025 to 31 Dec 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="8">
+        <f>"Highest profit factor: SL "&amp;INDEX(Grid_Search!$A$2:$A$17,MATCH(MAX(Grid_Search!$G$2:$G$17),Grid_Search!$G$2:$G$17,0))&amp;" / TP "&amp;INDEX(Grid_Search!$B$2:$B$17,MATCH(MAX(Grid_Search!$G$2:$G$17),Grid_Search!$G$2:$G$17,0))&amp;"  (profit factor "&amp;TEXT(MAX(Grid_Search!$G$2:$G$17),"0.00")&amp;" on "&amp;INDEX(Grid_Search!$C$2:$C$17,MATCH(MAX(Grid_Search!$G$2:$G$17),Grid_Search!$G$2:$G$17,0))&amp;" trades)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Profit factor</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Win rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>SL \ TP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>SL \ TP</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>Grid_Search!G16</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>Grid_Search!G15</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>Grid_Search!G13</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>Grid_Search!G17</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="I7" s="12">
+        <f>Grid_Search!D16</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>Grid_Search!D15</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>Grid_Search!D13</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>Grid_Search!D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>Grid_Search!G12</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>Grid_Search!G9</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>Grid_Search!G8</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>Grid_Search!G14</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I8" s="12">
+        <f>Grid_Search!D12</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>Grid_Search!D9</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>Grid_Search!D8</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>Grid_Search!D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>Grid_Search!G10</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>Grid_Search!G6</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>Grid_Search!G4</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>Grid_Search!G11</f>
+        <v/>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="I9" s="12">
+        <f>Grid_Search!D10</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>Grid_Search!D6</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>Grid_Search!D4</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>Grid_Search!D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="B10" s="13">
+        <f>Grid_Search!G5</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>Grid_Search!G3</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>Grid_Search!G2</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>Grid_Search!G7</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I10" s="14">
+        <f>Grid_Search!D5</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>Grid_Search!D3</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>Grid_Search!D2</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>Grid_Search!D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Sum of trade returns (%)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Number of trades</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SL \ TP</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>SL \ TP</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>Grid_Search!H16</f>
+        <v/>
+      </c>
+      <c r="C16" s="12">
+        <f>Grid_Search!H15</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>Grid_Search!H13</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>Grid_Search!H17</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="I16" s="15">
+        <f>Grid_Search!C16</f>
+        <v/>
+      </c>
+      <c r="J16" s="15">
+        <f>Grid_Search!C15</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>Grid_Search!C13</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
+        <f>Grid_Search!C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>Grid_Search!H12</f>
+        <v/>
+      </c>
+      <c r="C17" s="12">
+        <f>Grid_Search!H9</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>Grid_Search!H8</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>Grid_Search!H14</f>
+        <v/>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I17" s="15">
+        <f>Grid_Search!C12</f>
+        <v/>
+      </c>
+      <c r="J17" s="15">
+        <f>Grid_Search!C9</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>Grid_Search!C8</f>
+        <v/>
+      </c>
+      <c r="L17" s="15">
+        <f>Grid_Search!C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>Grid_Search!H10</f>
+        <v/>
+      </c>
+      <c r="C18" s="12">
+        <f>Grid_Search!H6</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>Grid_Search!H4</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>Grid_Search!H11</f>
+        <v/>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="I18" s="15">
+        <f>Grid_Search!C10</f>
+        <v/>
+      </c>
+      <c r="J18" s="15">
+        <f>Grid_Search!C6</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>Grid_Search!C4</f>
+        <v/>
+      </c>
+      <c r="L18" s="15">
+        <f>Grid_Search!C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <f>Grid_Search!H5</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>Grid_Search!H3</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>Grid_Search!H2</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>Grid_Search!H7</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I19" s="16">
+        <f>Grid_Search!C5</f>
+        <v/>
+      </c>
+      <c r="J19" s="15">
+        <f>Grid_Search!C3</f>
+        <v/>
+      </c>
+      <c r="K19" s="15">
+        <f>Grid_Search!C2</f>
+        <v/>
+      </c>
+      <c r="L19" s="15">
+        <f>Grid_Search!C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Orange outline = the pair currently set in strategy_config.py (SL 10% / TP 5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Every cell is a link to the Grid_Search sheet. Pairs with fewer than about 30 trades are statistically weak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Sum of trade returns adds up per-trade percentages; it is not portfolio growth.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B7:E10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
+        <color rgb="00F2B8B8"/>
+        <color rgb="00EEEEEA"/>
+        <color rgb="006DA7EC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:L10">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00E3EEFB"/>
+        <color rgb="006DA7EC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:E19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00E3EEFB"/>
+        <color rgb="006DA7EC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:L19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00E3EEFB"/>
+        <color rgb="006DA7EC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/results/Optimization.xlsx
+++ b/results/Optimization.xlsx
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>32</v>
+        <v>257</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>71.88</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>8.210000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-8.74</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>110.33</v>
+        <v>587.47</v>
       </c>
     </row>
     <row r="3">
@@ -652,82 +652,82 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>33</v>
+        <v>263</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>72.73</v>
+        <v>74.14</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7.09</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>-8.74</v>
+        <v>-9.66</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>512.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>63.16</v>
+        <v>70.47</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.279999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-7.98</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>86.84</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>73.53</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.41</v>
+        <v>7.45</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-8.74</v>
+        <v>-7.19</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>56.56</v>
+        <v>522.4400000000001</v>
       </c>
     </row>
     <row r="6">
@@ -738,26 +738,26 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>59.93</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.2</v>
+        <v>7.78</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.98</v>
+        <v>-7.19</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>68.12</v>
+        <v>528.52</v>
       </c>
     </row>
     <row r="7">
@@ -768,122 +768,122 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>66.67</v>
+        <v>77.67</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-9.77</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1.59</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>57.27</v>
+        <v>379.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>46</v>
+        <v>313</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>52.17</v>
+        <v>63.58</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.609999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.17</v>
+        <v>-7.19</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>71.01000000000001</v>
+        <v>444.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
       <c r="C9" s="3" t="n">
-        <v>47</v>
+        <v>353</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>53.19</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.52</v>
+        <v>4.54</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.17</v>
+        <v>-7.19</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>52.29</v>
+        <v>382.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>41</v>
+        <v>360</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.45</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.98</v>
+        <v>-5.19</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>35.35</v>
+        <v>421.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -892,52 +892,52 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>36</v>
+        <v>358</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>58.33</v>
+        <v>45.81</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.84</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.720000000000001</v>
+        <v>-5.19</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>33.79</v>
+        <v>391.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>49</v>
+        <v>480</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>57.14</v>
+        <v>33.96</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.79</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.19</v>
+        <v>-3.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>32.19</v>
+        <v>394.18</v>
       </c>
     </row>
     <row r="13">
@@ -948,26 +948,26 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>53</v>
+        <v>477</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>33.96</v>
+        <v>32.91</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.05</v>
+        <v>9.02</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.31</v>
+        <v>-3.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>30</v>
+        <v>393.13</v>
       </c>
     </row>
     <row r="14">
@@ -978,26 +978,26 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>44</v>
+        <v>369</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>47.73</v>
+        <v>50.14</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.73</v>
+        <v>-5.19</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>17.96</v>
+        <v>300.02</v>
       </c>
     </row>
     <row r="15">
@@ -1012,28 +1012,28 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>54</v>
+        <v>491</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>35.19</v>
+        <v>36.46</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.31</v>
+        <v>-3.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.95</v>
+        <v>275.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1042,22 +1042,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>55</v>
+        <v>402</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>40</v>
+        <v>57.96</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.14</v>
+        <v>4.67</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.35</v>
+        <v>-5.19</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-8.42</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="17">
@@ -1068,26 +1068,26 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51</v>
+        <v>534</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>27.45</v>
+        <v>44.19</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.34</v>
+        <v>4.74</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.69</v>
+        <v>-3.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-42.86</v>
+        <v>165.65</v>
       </c>
     </row>
   </sheetData>
@@ -1167,7 +1167,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Tuned on 01 Jan 2024 to 31 Dec 2024. The chosen pair is then tested on 01 Jan 2025 to 31 Dec 2025.</t>
+          <t>Tuned on 2024-01-01 to 2025-12-31. The chosen pair is then tested on 2025-01-01 to 2030-01-01.</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>Grid_Search!G16</f>
+        <f>Grid_Search!G17</f>
         <v/>
       </c>
       <c r="C7" s="11">
@@ -1256,20 +1256,20 @@
         <v/>
       </c>
       <c r="D7" s="11">
+        <f>Grid_Search!G12</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
         <f>Grid_Search!G13</f>
         <v/>
       </c>
-      <c r="E7" s="11">
-        <f>Grid_Search!G17</f>
-        <v/>
-      </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
       <c r="I7" s="12">
-        <f>Grid_Search!D16</f>
+        <f>Grid_Search!D17</f>
         <v/>
       </c>
       <c r="J7" s="12">
@@ -1277,11 +1277,11 @@
         <v/>
       </c>
       <c r="K7" s="12">
+        <f>Grid_Search!D12</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
         <f>Grid_Search!D13</f>
-        <v/>
-      </c>
-      <c r="L7" s="12">
-        <f>Grid_Search!D17</f>
         <v/>
       </c>
     </row>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>Grid_Search!G12</f>
+        <f>Grid_Search!G16</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>Grid_Search!G9</f>
+        <f>Grid_Search!G14</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>Grid_Search!G8</f>
+        <f>Grid_Search!G10</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>Grid_Search!G14</f>
+        <f>Grid_Search!G11</f>
         <v/>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1313,19 +1313,19 @@
         </is>
       </c>
       <c r="I8" s="12">
-        <f>Grid_Search!D12</f>
+        <f>Grid_Search!D16</f>
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>Grid_Search!D9</f>
+        <f>Grid_Search!D14</f>
         <v/>
       </c>
       <c r="K8" s="12">
-        <f>Grid_Search!D8</f>
+        <f>Grid_Search!D10</f>
         <v/>
       </c>
       <c r="L8" s="12">
-        <f>Grid_Search!D14</f>
+        <f>Grid_Search!D11</f>
         <v/>
       </c>
     </row>
@@ -1336,40 +1336,40 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>Grid_Search!G10</f>
+        <f>Grid_Search!G9</f>
         <v/>
       </c>
       <c r="C9" s="11">
+        <f>Grid_Search!G8</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>Grid_Search!G5</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
         <f>Grid_Search!G6</f>
         <v/>
       </c>
-      <c r="D9" s="11">
-        <f>Grid_Search!G4</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
-        <f>Grid_Search!G11</f>
-        <v/>
-      </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
       <c r="I9" s="12">
-        <f>Grid_Search!D10</f>
+        <f>Grid_Search!D9</f>
         <v/>
       </c>
       <c r="J9" s="12">
+        <f>Grid_Search!D8</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>Grid_Search!D5</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
         <f>Grid_Search!D6</f>
-        <v/>
-      </c>
-      <c r="K9" s="12">
-        <f>Grid_Search!D4</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>Grid_Search!D11</f>
         <v/>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>Grid_Search!G5</f>
+        <f>Grid_Search!G7</f>
         <v/>
       </c>
       <c r="C10" s="11">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>Grid_Search!G7</f>
+        <f>Grid_Search!G4</f>
         <v/>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="I10" s="14">
-        <f>Grid_Search!D5</f>
+        <f>Grid_Search!D7</f>
         <v/>
       </c>
       <c r="J10" s="12">
@@ -1413,7 +1413,7 @@
         <v/>
       </c>
       <c r="L10" s="12">
-        <f>Grid_Search!D7</f>
+        <f>Grid_Search!D4</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>Grid_Search!H16</f>
+        <f>Grid_Search!H17</f>
         <v/>
       </c>
       <c r="C16" s="12">
@@ -1496,20 +1496,20 @@
         <v/>
       </c>
       <c r="D16" s="12">
+        <f>Grid_Search!H12</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
         <f>Grid_Search!H13</f>
         <v/>
       </c>
-      <c r="E16" s="12">
-        <f>Grid_Search!H17</f>
-        <v/>
-      </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
       <c r="I16" s="15">
-        <f>Grid_Search!C16</f>
+        <f>Grid_Search!C17</f>
         <v/>
       </c>
       <c r="J16" s="15">
@@ -1517,11 +1517,11 @@
         <v/>
       </c>
       <c r="K16" s="15">
+        <f>Grid_Search!C12</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
         <f>Grid_Search!C13</f>
-        <v/>
-      </c>
-      <c r="L16" s="15">
-        <f>Grid_Search!C17</f>
         <v/>
       </c>
     </row>
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="B17" s="12">
-        <f>Grid_Search!H12</f>
+        <f>Grid_Search!H16</f>
         <v/>
       </c>
       <c r="C17" s="12">
-        <f>Grid_Search!H9</f>
+        <f>Grid_Search!H14</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>Grid_Search!H8</f>
+        <f>Grid_Search!H10</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>Grid_Search!H14</f>
+        <f>Grid_Search!H11</f>
         <v/>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -1553,19 +1553,19 @@
         </is>
       </c>
       <c r="I17" s="15">
-        <f>Grid_Search!C12</f>
+        <f>Grid_Search!C16</f>
         <v/>
       </c>
       <c r="J17" s="15">
-        <f>Grid_Search!C9</f>
+        <f>Grid_Search!C14</f>
         <v/>
       </c>
       <c r="K17" s="15">
-        <f>Grid_Search!C8</f>
+        <f>Grid_Search!C10</f>
         <v/>
       </c>
       <c r="L17" s="15">
-        <f>Grid_Search!C14</f>
+        <f>Grid_Search!C11</f>
         <v/>
       </c>
     </row>
@@ -1576,40 +1576,40 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>Grid_Search!H10</f>
+        <f>Grid_Search!H9</f>
         <v/>
       </c>
       <c r="C18" s="12">
+        <f>Grid_Search!H8</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>Grid_Search!H5</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
         <f>Grid_Search!H6</f>
         <v/>
       </c>
-      <c r="D18" s="12">
-        <f>Grid_Search!H4</f>
-        <v/>
-      </c>
-      <c r="E18" s="12">
-        <f>Grid_Search!H11</f>
-        <v/>
-      </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
       <c r="I18" s="15">
-        <f>Grid_Search!C10</f>
+        <f>Grid_Search!C9</f>
         <v/>
       </c>
       <c r="J18" s="15">
+        <f>Grid_Search!C8</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>Grid_Search!C5</f>
+        <v/>
+      </c>
+      <c r="L18" s="15">
         <f>Grid_Search!C6</f>
-        <v/>
-      </c>
-      <c r="K18" s="15">
-        <f>Grid_Search!C4</f>
-        <v/>
-      </c>
-      <c r="L18" s="15">
-        <f>Grid_Search!C11</f>
         <v/>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B19" s="14">
-        <f>Grid_Search!H5</f>
+        <f>Grid_Search!H7</f>
         <v/>
       </c>
       <c r="C19" s="12">
@@ -1632,7 +1632,7 @@
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>Grid_Search!H7</f>
+        <f>Grid_Search!H4</f>
         <v/>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="I19" s="16">
-        <f>Grid_Search!C5</f>
+        <f>Grid_Search!C7</f>
         <v/>
       </c>
       <c r="J19" s="15">
@@ -1653,7 +1653,7 @@
         <v/>
       </c>
       <c r="L19" s="15">
-        <f>Grid_Search!C7</f>
+        <f>Grid_Search!C4</f>
         <v/>
       </c>
     </row>
@@ -1686,10 +1686,8 @@
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
         <cfvo type="max"/>
-        <color rgb="00F2B8B8"/>
-        <color rgb="00EEEEEA"/>
+        <color rgb="00E3EEFB"/>
         <color rgb="006DA7EC"/>
       </colorScale>
     </cfRule>
